--- a/機能設計書 NamedPipeServer Client.xlsx
+++ b/機能設計書 NamedPipeServer Client.xlsx
@@ -16,6 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ログ仕様" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="エラー処理仕様" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="制約・前提条件" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フロー図" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="シーケンス図" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フロー図1" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="シーケンス図1" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -162,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -184,11 +188,55 @@
         <color rgb="00B8CCE4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -265,6 +313,14 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -339,6 +395,291 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="8001000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="7429500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>135</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="6858000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="4572000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4095750" cy="8191500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4095750" cy="7620000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>138</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4095750" cy="7048500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7429500" cy="6286500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6286500" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -649,6 +990,11 @@
           <t>機　能　設　計　書</t>
         </is>
       </c>
+      <c r="B2" s="26" t="n"/>
+      <c r="C2" s="26" t="n"/>
+      <c r="D2" s="26" t="n"/>
+      <c r="E2" s="26" t="n"/>
+      <c r="F2" s="27" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -656,6 +1002,11 @@
           <t>名前付きパイプサーバー / クライアント（PowerShell 5.1 + Oracle ODP.NET）</t>
         </is>
       </c>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="27" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1"/>
     <row r="6" ht="22" customHeight="1">
@@ -669,6 +1020,9 @@
           <t>NamedPipeServer.ps1 / NamedPipeClient.ps1</t>
         </is>
       </c>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="27" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
@@ -681,6 +1035,9 @@
           <t>PowerShell 5.1 / Windows OS</t>
         </is>
       </c>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="27" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
@@ -693,6 +1050,9 @@
           <t>Oracle.ManagedDataAccess.dll (ODP.NET Managed)</t>
         </is>
       </c>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="27" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
@@ -705,6 +1065,9 @@
           <t>2026-03-13</t>
         </is>
       </c>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="27" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="3" t="inlineStr">
@@ -717,6 +1080,9 @@
           <t>1.0</t>
         </is>
       </c>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="27" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
@@ -729,6 +1095,9 @@
           <t>―</t>
         </is>
       </c>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="27" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="3" t="inlineStr">
@@ -741,6 +1110,9 @@
           <t>―</t>
         </is>
       </c>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -755,6 +1127,878 @@
     <mergeCell ref="C10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L135"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>フロー図</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="26" t="n"/>
+      <c r="G1" s="26" t="n"/>
+      <c r="H1" s="26" t="n"/>
+      <c r="I1" s="26" t="n"/>
+      <c r="J1" s="26" t="n"/>
+      <c r="K1" s="26" t="n"/>
+      <c r="L1" s="27" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>1. サーバー起動・停止フロー (-Action Start / Stop)</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="26" t="n"/>
+      <c r="G3" s="26" t="n"/>
+      <c r="H3" s="26" t="n"/>
+      <c r="I3" s="26" t="n"/>
+      <c r="J3" s="26" t="n"/>
+      <c r="K3" s="26" t="n"/>
+      <c r="L3" s="27" t="n"/>
+    </row>
+    <row r="4" ht="13" customHeight="1"/>
+    <row r="5" ht="13" customHeight="1"/>
+    <row r="6" ht="13" customHeight="1"/>
+    <row r="7" ht="13" customHeight="1"/>
+    <row r="8" ht="13" customHeight="1"/>
+    <row r="9" ht="13" customHeight="1"/>
+    <row r="10" ht="13" customHeight="1"/>
+    <row r="11" ht="13" customHeight="1"/>
+    <row r="12" ht="13" customHeight="1"/>
+    <row r="13" ht="13" customHeight="1"/>
+    <row r="14" ht="13" customHeight="1"/>
+    <row r="15" ht="13" customHeight="1"/>
+    <row r="16" ht="13" customHeight="1"/>
+    <row r="17" ht="13" customHeight="1"/>
+    <row r="18" ht="13" customHeight="1"/>
+    <row r="19" ht="13" customHeight="1"/>
+    <row r="20" ht="13" customHeight="1"/>
+    <row r="21" ht="13" customHeight="1"/>
+    <row r="22" ht="13" customHeight="1"/>
+    <row r="23" ht="13" customHeight="1"/>
+    <row r="24" ht="13" customHeight="1"/>
+    <row r="25" ht="13" customHeight="1"/>
+    <row r="26" ht="13" customHeight="1"/>
+    <row r="27" ht="13" customHeight="1"/>
+    <row r="28" ht="13" customHeight="1"/>
+    <row r="29" ht="13" customHeight="1"/>
+    <row r="30" ht="13" customHeight="1"/>
+    <row r="31" ht="13" customHeight="1"/>
+    <row r="32" ht="13" customHeight="1"/>
+    <row r="33" ht="13" customHeight="1"/>
+    <row r="34" ht="13" customHeight="1"/>
+    <row r="35" ht="13" customHeight="1"/>
+    <row r="36" ht="13" customHeight="1"/>
+    <row r="37" ht="13" customHeight="1"/>
+    <row r="38" ht="13" customHeight="1"/>
+    <row r="39" ht="13" customHeight="1"/>
+    <row r="40" ht="13" customHeight="1"/>
+    <row r="41" ht="13" customHeight="1"/>
+    <row r="42" ht="13" customHeight="1"/>
+    <row r="43" ht="13" customHeight="1"/>
+    <row r="44" ht="13" customHeight="1"/>
+    <row r="45" ht="13" customHeight="1"/>
+    <row r="46" ht="13" customHeight="1"/>
+    <row r="47" ht="13" customHeight="1"/>
+    <row r="48" ht="13" customHeight="1"/>
+    <row r="49" ht="13" customHeight="1"/>
+    <row r="50" ht="13" customHeight="1"/>
+    <row r="51" ht="13" customHeight="1"/>
+    <row r="52" ht="13" customHeight="1"/>
+    <row r="53" ht="13" customHeight="1"/>
+    <row r="54" ht="13" customHeight="1"/>
+    <row r="55" ht="13" customHeight="1"/>
+    <row r="56" ht="13" customHeight="1"/>
+    <row r="57" ht="13" customHeight="1"/>
+    <row r="58" ht="13" customHeight="1"/>
+    <row r="59" ht="13" customHeight="1"/>
+    <row r="60" ht="13" customHeight="1"/>
+    <row r="61" ht="13" customHeight="1"/>
+    <row r="62" ht="13" customHeight="1"/>
+    <row r="63" ht="13" customHeight="1"/>
+    <row r="64" ht="13" customHeight="1"/>
+    <row r="65" ht="13" customHeight="1"/>
+    <row r="66" ht="13" customHeight="1"/>
+    <row r="67" ht="13" customHeight="1"/>
+    <row r="68" ht="13" customHeight="1"/>
+    <row r="69" ht="13" customHeight="1"/>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>2. サーバー内部実行フロー (_Run 接続受付ループ)</t>
+        </is>
+      </c>
+      <c r="B71" s="26" t="n"/>
+      <c r="C71" s="26" t="n"/>
+      <c r="D71" s="26" t="n"/>
+      <c r="E71" s="26" t="n"/>
+      <c r="F71" s="26" t="n"/>
+      <c r="G71" s="26" t="n"/>
+      <c r="H71" s="26" t="n"/>
+      <c r="I71" s="26" t="n"/>
+      <c r="J71" s="26" t="n"/>
+      <c r="K71" s="26" t="n"/>
+      <c r="L71" s="27" t="n"/>
+    </row>
+    <row r="72" ht="13" customHeight="1"/>
+    <row r="73" ht="13" customHeight="1"/>
+    <row r="74" ht="13" customHeight="1"/>
+    <row r="75" ht="13" customHeight="1"/>
+    <row r="76" ht="13" customHeight="1"/>
+    <row r="77" ht="13" customHeight="1"/>
+    <row r="78" ht="13" customHeight="1"/>
+    <row r="79" ht="13" customHeight="1"/>
+    <row r="80" ht="13" customHeight="1"/>
+    <row r="81" ht="13" customHeight="1"/>
+    <row r="82" ht="13" customHeight="1"/>
+    <row r="83" ht="13" customHeight="1"/>
+    <row r="84" ht="13" customHeight="1"/>
+    <row r="85" ht="13" customHeight="1"/>
+    <row r="86" ht="13" customHeight="1"/>
+    <row r="87" ht="13" customHeight="1"/>
+    <row r="88" ht="13" customHeight="1"/>
+    <row r="89" ht="13" customHeight="1"/>
+    <row r="90" ht="13" customHeight="1"/>
+    <row r="91" ht="13" customHeight="1"/>
+    <row r="92" ht="13" customHeight="1"/>
+    <row r="93" ht="13" customHeight="1"/>
+    <row r="94" ht="13" customHeight="1"/>
+    <row r="95" ht="13" customHeight="1"/>
+    <row r="96" ht="13" customHeight="1"/>
+    <row r="97" ht="13" customHeight="1"/>
+    <row r="98" ht="13" customHeight="1"/>
+    <row r="99" ht="13" customHeight="1"/>
+    <row r="100" ht="13" customHeight="1"/>
+    <row r="101" ht="13" customHeight="1"/>
+    <row r="102" ht="13" customHeight="1"/>
+    <row r="103" ht="13" customHeight="1"/>
+    <row r="104" ht="13" customHeight="1"/>
+    <row r="105" ht="13" customHeight="1"/>
+    <row r="106" ht="13" customHeight="1"/>
+    <row r="107" ht="13" customHeight="1"/>
+    <row r="108" ht="13" customHeight="1"/>
+    <row r="109" ht="13" customHeight="1"/>
+    <row r="110" ht="13" customHeight="1"/>
+    <row r="111" ht="13" customHeight="1"/>
+    <row r="112" ht="13" customHeight="1"/>
+    <row r="113" ht="13" customHeight="1"/>
+    <row r="114" ht="13" customHeight="1"/>
+    <row r="115" ht="13" customHeight="1"/>
+    <row r="116" ht="13" customHeight="1"/>
+    <row r="117" ht="13" customHeight="1"/>
+    <row r="118" ht="13" customHeight="1"/>
+    <row r="119" ht="13" customHeight="1"/>
+    <row r="120" ht="13" customHeight="1"/>
+    <row r="121" ht="13" customHeight="1"/>
+    <row r="122" ht="13" customHeight="1"/>
+    <row r="123" ht="13" customHeight="1"/>
+    <row r="124" ht="13" customHeight="1"/>
+    <row r="125" ht="13" customHeight="1"/>
+    <row r="126" ht="13" customHeight="1"/>
+    <row r="127" ht="13" customHeight="1"/>
+    <row r="128" ht="13" customHeight="1"/>
+    <row r="129" ht="13" customHeight="1"/>
+    <row r="130" ht="13" customHeight="1"/>
+    <row r="131" ht="13" customHeight="1"/>
+    <row r="132" ht="13" customHeight="1"/>
+    <row r="133" ht="13" customHeight="1"/>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="29" t="inlineStr">
+        <is>
+          <t>3. クライアント接続リトライフロー</t>
+        </is>
+      </c>
+      <c r="B135" s="26" t="n"/>
+      <c r="C135" s="26" t="n"/>
+      <c r="D135" s="26" t="n"/>
+      <c r="E135" s="26" t="n"/>
+      <c r="F135" s="26" t="n"/>
+      <c r="G135" s="26" t="n"/>
+      <c r="H135" s="26" t="n"/>
+      <c r="I135" s="26" t="n"/>
+      <c r="J135" s="26" t="n"/>
+      <c r="K135" s="26" t="n"/>
+      <c r="L135" s="27" t="n"/>
+    </row>
+    <row r="136" ht="13" customHeight="1"/>
+    <row r="137" ht="13" customHeight="1"/>
+    <row r="138" ht="13" customHeight="1"/>
+    <row r="139" ht="13" customHeight="1"/>
+    <row r="140" ht="13" customHeight="1"/>
+    <row r="141" ht="13" customHeight="1"/>
+    <row r="142" ht="13" customHeight="1"/>
+    <row r="143" ht="13" customHeight="1"/>
+    <row r="144" ht="13" customHeight="1"/>
+    <row r="145" ht="13" customHeight="1"/>
+    <row r="146" ht="13" customHeight="1"/>
+    <row r="147" ht="13" customHeight="1"/>
+    <row r="148" ht="13" customHeight="1"/>
+    <row r="149" ht="13" customHeight="1"/>
+    <row r="150" ht="13" customHeight="1"/>
+    <row r="151" ht="13" customHeight="1"/>
+    <row r="152" ht="13" customHeight="1"/>
+    <row r="153" ht="13" customHeight="1"/>
+    <row r="154" ht="13" customHeight="1"/>
+    <row r="155" ht="13" customHeight="1"/>
+    <row r="156" ht="13" customHeight="1"/>
+    <row r="157" ht="13" customHeight="1"/>
+    <row r="158" ht="13" customHeight="1"/>
+    <row r="159" ht="13" customHeight="1"/>
+    <row r="160" ht="13" customHeight="1"/>
+    <row r="161" ht="13" customHeight="1"/>
+    <row r="162" ht="13" customHeight="1"/>
+    <row r="163" ht="13" customHeight="1"/>
+    <row r="164" ht="13" customHeight="1"/>
+    <row r="165" ht="13" customHeight="1"/>
+    <row r="166" ht="13" customHeight="1"/>
+    <row r="167" ht="13" customHeight="1"/>
+    <row r="168" ht="13" customHeight="1"/>
+    <row r="169" ht="13" customHeight="1"/>
+    <row r="170" ht="13" customHeight="1"/>
+    <row r="171" ht="13" customHeight="1"/>
+    <row r="172" ht="13" customHeight="1"/>
+    <row r="173" ht="13" customHeight="1"/>
+    <row r="174" ht="13" customHeight="1"/>
+    <row r="175" ht="13" customHeight="1"/>
+    <row r="176" ht="13" customHeight="1"/>
+    <row r="177" ht="13" customHeight="1"/>
+    <row r="178" ht="13" customHeight="1"/>
+    <row r="179" ht="13" customHeight="1"/>
+    <row r="180" ht="13" customHeight="1"/>
+    <row r="181" ht="13" customHeight="1"/>
+    <row r="182" ht="13" customHeight="1"/>
+    <row r="183" ht="13" customHeight="1"/>
+    <row r="184" ht="13" customHeight="1"/>
+    <row r="185" ht="13" customHeight="1"/>
+    <row r="186" ht="13" customHeight="1"/>
+    <row r="187" ht="13" customHeight="1"/>
+    <row r="188" ht="13" customHeight="1"/>
+    <row r="189" ht="13" customHeight="1"/>
+    <row r="190" ht="13" customHeight="1"/>
+    <row r="191" ht="13" customHeight="1"/>
+    <row r="192" ht="13" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A135:L135"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A71:L71"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>シーケンス図</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="26" t="n"/>
+      <c r="G1" s="26" t="n"/>
+      <c r="H1" s="26" t="n"/>
+      <c r="I1" s="26" t="n"/>
+      <c r="J1" s="26" t="n"/>
+      <c r="K1" s="26" t="n"/>
+      <c r="L1" s="27" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>1. 接続・通信・停止 シーケンス図（全体）</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="26" t="n"/>
+      <c r="G3" s="26" t="n"/>
+      <c r="H3" s="26" t="n"/>
+      <c r="I3" s="26" t="n"/>
+      <c r="J3" s="26" t="n"/>
+      <c r="K3" s="26" t="n"/>
+      <c r="L3" s="27" t="n"/>
+    </row>
+    <row r="4" ht="13" customHeight="1"/>
+    <row r="5" ht="13" customHeight="1"/>
+    <row r="6" ht="13" customHeight="1"/>
+    <row r="7" ht="13" customHeight="1"/>
+    <row r="8" ht="13" customHeight="1"/>
+    <row r="9" ht="13" customHeight="1"/>
+    <row r="10" ht="13" customHeight="1"/>
+    <row r="11" ht="13" customHeight="1"/>
+    <row r="12" ht="13" customHeight="1"/>
+    <row r="13" ht="13" customHeight="1"/>
+    <row r="14" ht="13" customHeight="1"/>
+    <row r="15" ht="13" customHeight="1"/>
+    <row r="16" ht="13" customHeight="1"/>
+    <row r="17" ht="13" customHeight="1"/>
+    <row r="18" ht="13" customHeight="1"/>
+    <row r="19" ht="13" customHeight="1"/>
+    <row r="20" ht="13" customHeight="1"/>
+    <row r="21" ht="13" customHeight="1"/>
+    <row r="22" ht="13" customHeight="1"/>
+    <row r="23" ht="13" customHeight="1"/>
+    <row r="24" ht="13" customHeight="1"/>
+    <row r="25" ht="13" customHeight="1"/>
+    <row r="26" ht="13" customHeight="1"/>
+    <row r="27" ht="13" customHeight="1"/>
+    <row r="28" ht="13" customHeight="1"/>
+    <row r="29" ht="13" customHeight="1"/>
+    <row r="30" ht="13" customHeight="1"/>
+    <row r="31" ht="13" customHeight="1"/>
+    <row r="32" ht="13" customHeight="1"/>
+    <row r="33" ht="13" customHeight="1"/>
+    <row r="34" ht="13" customHeight="1"/>
+    <row r="35" ht="13" customHeight="1"/>
+    <row r="36" ht="13" customHeight="1"/>
+    <row r="37" ht="13" customHeight="1"/>
+    <row r="38" ht="13" customHeight="1"/>
+    <row r="39" ht="13" customHeight="1"/>
+    <row r="40" ht="13" customHeight="1"/>
+    <row r="41" ht="13" customHeight="1"/>
+    <row r="42" ht="13" customHeight="1"/>
+    <row r="43" ht="13" customHeight="1"/>
+    <row r="44" ht="13" customHeight="1"/>
+    <row r="45" ht="13" customHeight="1"/>
+    <row r="46" ht="13" customHeight="1"/>
+    <row r="47" ht="13" customHeight="1"/>
+    <row r="48" ht="13" customHeight="1"/>
+    <row r="49" ht="13" customHeight="1"/>
+    <row r="50" ht="13" customHeight="1"/>
+    <row r="51" ht="13" customHeight="1"/>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="29" t="inlineStr">
+        <is>
+          <t>2. クライアント リトライ シーケンス図</t>
+        </is>
+      </c>
+      <c r="B53" s="26" t="n"/>
+      <c r="C53" s="26" t="n"/>
+      <c r="D53" s="26" t="n"/>
+      <c r="E53" s="26" t="n"/>
+      <c r="F53" s="26" t="n"/>
+      <c r="G53" s="26" t="n"/>
+      <c r="H53" s="26" t="n"/>
+      <c r="I53" s="26" t="n"/>
+      <c r="J53" s="26" t="n"/>
+      <c r="K53" s="26" t="n"/>
+      <c r="L53" s="27" t="n"/>
+    </row>
+    <row r="54" ht="13" customHeight="1"/>
+    <row r="55" ht="13" customHeight="1"/>
+    <row r="56" ht="13" customHeight="1"/>
+    <row r="57" ht="13" customHeight="1"/>
+    <row r="58" ht="13" customHeight="1"/>
+    <row r="59" ht="13" customHeight="1"/>
+    <row r="60" ht="13" customHeight="1"/>
+    <row r="61" ht="13" customHeight="1"/>
+    <row r="62" ht="13" customHeight="1"/>
+    <row r="63" ht="13" customHeight="1"/>
+    <row r="64" ht="13" customHeight="1"/>
+    <row r="65" ht="13" customHeight="1"/>
+    <row r="66" ht="13" customHeight="1"/>
+    <row r="67" ht="13" customHeight="1"/>
+    <row r="68" ht="13" customHeight="1"/>
+    <row r="69" ht="13" customHeight="1"/>
+    <row r="70" ht="13" customHeight="1"/>
+    <row r="71" ht="13" customHeight="1"/>
+    <row r="72" ht="13" customHeight="1"/>
+    <row r="73" ht="13" customHeight="1"/>
+    <row r="74" ht="13" customHeight="1"/>
+    <row r="75" ht="13" customHeight="1"/>
+    <row r="76" ht="13" customHeight="1"/>
+    <row r="77" ht="13" customHeight="1"/>
+    <row r="78" ht="13" customHeight="1"/>
+    <row r="79" ht="13" customHeight="1"/>
+    <row r="80" ht="13" customHeight="1"/>
+    <row r="81" ht="13" customHeight="1"/>
+    <row r="82" ht="13" customHeight="1"/>
+    <row r="83" ht="13" customHeight="1"/>
+    <row r="84" ht="13" customHeight="1"/>
+    <row r="85" ht="13" customHeight="1"/>
+    <row r="86" ht="13" customHeight="1"/>
+    <row r="87" ht="13" customHeight="1"/>
+    <row r="88" ht="13" customHeight="1"/>
+    <row r="89" ht="13" customHeight="1"/>
+    <row r="90" ht="13" customHeight="1"/>
+    <row r="91" ht="13" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A53:L53"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L138"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>フロー図</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>1. サーバー起動・停止フロー (-Action Start / Stop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="13" customHeight="1"/>
+    <row r="5" ht="13" customHeight="1"/>
+    <row r="6" ht="13" customHeight="1"/>
+    <row r="7" ht="13" customHeight="1"/>
+    <row r="8" ht="13" customHeight="1"/>
+    <row r="9" ht="13" customHeight="1"/>
+    <row r="10" ht="13" customHeight="1"/>
+    <row r="11" ht="13" customHeight="1"/>
+    <row r="12" ht="13" customHeight="1"/>
+    <row r="13" ht="13" customHeight="1"/>
+    <row r="14" ht="13" customHeight="1"/>
+    <row r="15" ht="13" customHeight="1"/>
+    <row r="16" ht="13" customHeight="1"/>
+    <row r="17" ht="13" customHeight="1"/>
+    <row r="18" ht="13" customHeight="1"/>
+    <row r="19" ht="13" customHeight="1"/>
+    <row r="20" ht="13" customHeight="1"/>
+    <row r="21" ht="13" customHeight="1"/>
+    <row r="22" ht="13" customHeight="1"/>
+    <row r="23" ht="13" customHeight="1"/>
+    <row r="24" ht="13" customHeight="1"/>
+    <row r="25" ht="13" customHeight="1"/>
+    <row r="26" ht="13" customHeight="1"/>
+    <row r="27" ht="13" customHeight="1"/>
+    <row r="28" ht="13" customHeight="1"/>
+    <row r="29" ht="13" customHeight="1"/>
+    <row r="30" ht="13" customHeight="1"/>
+    <row r="31" ht="13" customHeight="1"/>
+    <row r="32" ht="13" customHeight="1"/>
+    <row r="33" ht="13" customHeight="1"/>
+    <row r="34" ht="13" customHeight="1"/>
+    <row r="35" ht="13" customHeight="1"/>
+    <row r="36" ht="13" customHeight="1"/>
+    <row r="37" ht="13" customHeight="1"/>
+    <row r="38" ht="13" customHeight="1"/>
+    <row r="39" ht="13" customHeight="1"/>
+    <row r="40" ht="13" customHeight="1"/>
+    <row r="41" ht="13" customHeight="1"/>
+    <row r="42" ht="13" customHeight="1"/>
+    <row r="43" ht="13" customHeight="1"/>
+    <row r="44" ht="13" customHeight="1"/>
+    <row r="45" ht="13" customHeight="1"/>
+    <row r="46" ht="13" customHeight="1"/>
+    <row r="47" ht="13" customHeight="1"/>
+    <row r="48" ht="13" customHeight="1"/>
+    <row r="49" ht="13" customHeight="1"/>
+    <row r="50" ht="13" customHeight="1"/>
+    <row r="51" ht="13" customHeight="1"/>
+    <row r="52" ht="13" customHeight="1"/>
+    <row r="53" ht="13" customHeight="1"/>
+    <row r="54" ht="13" customHeight="1"/>
+    <row r="55" ht="13" customHeight="1"/>
+    <row r="56" ht="13" customHeight="1"/>
+    <row r="57" ht="13" customHeight="1"/>
+    <row r="58" ht="13" customHeight="1"/>
+    <row r="59" ht="13" customHeight="1"/>
+    <row r="60" ht="13" customHeight="1"/>
+    <row r="61" ht="13" customHeight="1"/>
+    <row r="62" ht="13" customHeight="1"/>
+    <row r="63" ht="13" customHeight="1"/>
+    <row r="64" ht="13" customHeight="1"/>
+    <row r="65" ht="13" customHeight="1"/>
+    <row r="66" ht="13" customHeight="1"/>
+    <row r="67" ht="13" customHeight="1"/>
+    <row r="68" ht="13" customHeight="1"/>
+    <row r="69" ht="13" customHeight="1"/>
+    <row r="70" ht="13" customHeight="1"/>
+    <row r="71" ht="13" customHeight="1"/>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>2. サーバー内部実行フロー (_Run 接続受付ループ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="13" customHeight="1"/>
+    <row r="75" ht="13" customHeight="1"/>
+    <row r="76" ht="13" customHeight="1"/>
+    <row r="77" ht="13" customHeight="1"/>
+    <row r="78" ht="13" customHeight="1"/>
+    <row r="79" ht="13" customHeight="1"/>
+    <row r="80" ht="13" customHeight="1"/>
+    <row r="81" ht="13" customHeight="1"/>
+    <row r="82" ht="13" customHeight="1"/>
+    <row r="83" ht="13" customHeight="1"/>
+    <row r="84" ht="13" customHeight="1"/>
+    <row r="85" ht="13" customHeight="1"/>
+    <row r="86" ht="13" customHeight="1"/>
+    <row r="87" ht="13" customHeight="1"/>
+    <row r="88" ht="13" customHeight="1"/>
+    <row r="89" ht="13" customHeight="1"/>
+    <row r="90" ht="13" customHeight="1"/>
+    <row r="91" ht="13" customHeight="1"/>
+    <row r="92" ht="13" customHeight="1"/>
+    <row r="93" ht="13" customHeight="1"/>
+    <row r="94" ht="13" customHeight="1"/>
+    <row r="95" ht="13" customHeight="1"/>
+    <row r="96" ht="13" customHeight="1"/>
+    <row r="97" ht="13" customHeight="1"/>
+    <row r="98" ht="13" customHeight="1"/>
+    <row r="99" ht="13" customHeight="1"/>
+    <row r="100" ht="13" customHeight="1"/>
+    <row r="101" ht="13" customHeight="1"/>
+    <row r="102" ht="13" customHeight="1"/>
+    <row r="103" ht="13" customHeight="1"/>
+    <row r="104" ht="13" customHeight="1"/>
+    <row r="105" ht="13" customHeight="1"/>
+    <row r="106" ht="13" customHeight="1"/>
+    <row r="107" ht="13" customHeight="1"/>
+    <row r="108" ht="13" customHeight="1"/>
+    <row r="109" ht="13" customHeight="1"/>
+    <row r="110" ht="13" customHeight="1"/>
+    <row r="111" ht="13" customHeight="1"/>
+    <row r="112" ht="13" customHeight="1"/>
+    <row r="113" ht="13" customHeight="1"/>
+    <row r="114" ht="13" customHeight="1"/>
+    <row r="115" ht="13" customHeight="1"/>
+    <row r="116" ht="13" customHeight="1"/>
+    <row r="117" ht="13" customHeight="1"/>
+    <row r="118" ht="13" customHeight="1"/>
+    <row r="119" ht="13" customHeight="1"/>
+    <row r="120" ht="13" customHeight="1"/>
+    <row r="121" ht="13" customHeight="1"/>
+    <row r="122" ht="13" customHeight="1"/>
+    <row r="123" ht="13" customHeight="1"/>
+    <row r="124" ht="13" customHeight="1"/>
+    <row r="125" ht="13" customHeight="1"/>
+    <row r="126" ht="13" customHeight="1"/>
+    <row r="127" ht="13" customHeight="1"/>
+    <row r="128" ht="13" customHeight="1"/>
+    <row r="129" ht="13" customHeight="1"/>
+    <row r="130" ht="13" customHeight="1"/>
+    <row r="131" ht="13" customHeight="1"/>
+    <row r="132" ht="13" customHeight="1"/>
+    <row r="133" ht="13" customHeight="1"/>
+    <row r="134" ht="13" customHeight="1"/>
+    <row r="135" ht="13" customHeight="1"/>
+    <row r="136" ht="13" customHeight="1"/>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="29" t="inlineStr">
+        <is>
+          <t>3. クライアント接続リトライフロー</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="13" customHeight="1"/>
+    <row r="140" ht="13" customHeight="1"/>
+    <row r="141" ht="13" customHeight="1"/>
+    <row r="142" ht="13" customHeight="1"/>
+    <row r="143" ht="13" customHeight="1"/>
+    <row r="144" ht="13" customHeight="1"/>
+    <row r="145" ht="13" customHeight="1"/>
+    <row r="146" ht="13" customHeight="1"/>
+    <row r="147" ht="13" customHeight="1"/>
+    <row r="148" ht="13" customHeight="1"/>
+    <row r="149" ht="13" customHeight="1"/>
+    <row r="150" ht="13" customHeight="1"/>
+    <row r="151" ht="13" customHeight="1"/>
+    <row r="152" ht="13" customHeight="1"/>
+    <row r="153" ht="13" customHeight="1"/>
+    <row r="154" ht="13" customHeight="1"/>
+    <row r="155" ht="13" customHeight="1"/>
+    <row r="156" ht="13" customHeight="1"/>
+    <row r="157" ht="13" customHeight="1"/>
+    <row r="158" ht="13" customHeight="1"/>
+    <row r="159" ht="13" customHeight="1"/>
+    <row r="160" ht="13" customHeight="1"/>
+    <row r="161" ht="13" customHeight="1"/>
+    <row r="162" ht="13" customHeight="1"/>
+    <row r="163" ht="13" customHeight="1"/>
+    <row r="164" ht="13" customHeight="1"/>
+    <row r="165" ht="13" customHeight="1"/>
+    <row r="166" ht="13" customHeight="1"/>
+    <row r="167" ht="13" customHeight="1"/>
+    <row r="168" ht="13" customHeight="1"/>
+    <row r="169" ht="13" customHeight="1"/>
+    <row r="170" ht="13" customHeight="1"/>
+    <row r="171" ht="13" customHeight="1"/>
+    <row r="172" ht="13" customHeight="1"/>
+    <row r="173" ht="13" customHeight="1"/>
+    <row r="174" ht="13" customHeight="1"/>
+    <row r="175" ht="13" customHeight="1"/>
+    <row r="176" ht="13" customHeight="1"/>
+    <row r="177" ht="13" customHeight="1"/>
+    <row r="178" ht="13" customHeight="1"/>
+    <row r="179" ht="13" customHeight="1"/>
+    <row r="180" ht="13" customHeight="1"/>
+    <row r="181" ht="13" customHeight="1"/>
+    <row r="182" ht="13" customHeight="1"/>
+    <row r="183" ht="13" customHeight="1"/>
+    <row r="184" ht="13" customHeight="1"/>
+    <row r="185" ht="13" customHeight="1"/>
+    <row r="186" ht="13" customHeight="1"/>
+    <row r="187" ht="13" customHeight="1"/>
+    <row r="188" ht="13" customHeight="1"/>
+    <row r="189" ht="13" customHeight="1"/>
+    <row r="190" ht="13" customHeight="1"/>
+    <row r="191" ht="13" customHeight="1"/>
+    <row r="192" ht="13" customHeight="1"/>
+    <row r="193" ht="13" customHeight="1"/>
+    <row r="194" ht="13" customHeight="1"/>
+    <row r="195" ht="13" customHeight="1"/>
+    <row r="196" ht="13" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A73:L73"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A138:L138"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>シーケンス図</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>1. 接続・通信・停止 シーケンス図（全体フロー）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="13" customHeight="1"/>
+    <row r="5" ht="13" customHeight="1"/>
+    <row r="6" ht="13" customHeight="1"/>
+    <row r="7" ht="13" customHeight="1"/>
+    <row r="8" ht="13" customHeight="1"/>
+    <row r="9" ht="13" customHeight="1"/>
+    <row r="10" ht="13" customHeight="1"/>
+    <row r="11" ht="13" customHeight="1"/>
+    <row r="12" ht="13" customHeight="1"/>
+    <row r="13" ht="13" customHeight="1"/>
+    <row r="14" ht="13" customHeight="1"/>
+    <row r="15" ht="13" customHeight="1"/>
+    <row r="16" ht="13" customHeight="1"/>
+    <row r="17" ht="13" customHeight="1"/>
+    <row r="18" ht="13" customHeight="1"/>
+    <row r="19" ht="13" customHeight="1"/>
+    <row r="20" ht="13" customHeight="1"/>
+    <row r="21" ht="13" customHeight="1"/>
+    <row r="22" ht="13" customHeight="1"/>
+    <row r="23" ht="13" customHeight="1"/>
+    <row r="24" ht="13" customHeight="1"/>
+    <row r="25" ht="13" customHeight="1"/>
+    <row r="26" ht="13" customHeight="1"/>
+    <row r="27" ht="13" customHeight="1"/>
+    <row r="28" ht="13" customHeight="1"/>
+    <row r="29" ht="13" customHeight="1"/>
+    <row r="30" ht="13" customHeight="1"/>
+    <row r="31" ht="13" customHeight="1"/>
+    <row r="32" ht="13" customHeight="1"/>
+    <row r="33" ht="13" customHeight="1"/>
+    <row r="34" ht="13" customHeight="1"/>
+    <row r="35" ht="13" customHeight="1"/>
+    <row r="36" ht="13" customHeight="1"/>
+    <row r="37" ht="13" customHeight="1"/>
+    <row r="38" ht="13" customHeight="1"/>
+    <row r="39" ht="13" customHeight="1"/>
+    <row r="40" ht="13" customHeight="1"/>
+    <row r="41" ht="13" customHeight="1"/>
+    <row r="42" ht="13" customHeight="1"/>
+    <row r="43" ht="13" customHeight="1"/>
+    <row r="44" ht="13" customHeight="1"/>
+    <row r="45" ht="13" customHeight="1"/>
+    <row r="46" ht="13" customHeight="1"/>
+    <row r="47" ht="13" customHeight="1"/>
+    <row r="48" ht="13" customHeight="1"/>
+    <row r="49" ht="13" customHeight="1"/>
+    <row r="50" ht="13" customHeight="1"/>
+    <row r="51" ht="13" customHeight="1"/>
+    <row r="52" ht="13" customHeight="1"/>
+    <row r="53" ht="13" customHeight="1"/>
+    <row r="54" ht="13" customHeight="1"/>
+    <row r="55" ht="13" customHeight="1"/>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="29" t="inlineStr">
+        <is>
+          <t>2. クライアント リトライ シーケンス図</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="13" customHeight="1"/>
+    <row r="59" ht="13" customHeight="1"/>
+    <row r="60" ht="13" customHeight="1"/>
+    <row r="61" ht="13" customHeight="1"/>
+    <row r="62" ht="13" customHeight="1"/>
+    <row r="63" ht="13" customHeight="1"/>
+    <row r="64" ht="13" customHeight="1"/>
+    <row r="65" ht="13" customHeight="1"/>
+    <row r="66" ht="13" customHeight="1"/>
+    <row r="67" ht="13" customHeight="1"/>
+    <row r="68" ht="13" customHeight="1"/>
+    <row r="69" ht="13" customHeight="1"/>
+    <row r="70" ht="13" customHeight="1"/>
+    <row r="71" ht="13" customHeight="1"/>
+    <row r="72" ht="13" customHeight="1"/>
+    <row r="73" ht="13" customHeight="1"/>
+    <row r="74" ht="13" customHeight="1"/>
+    <row r="75" ht="13" customHeight="1"/>
+    <row r="76" ht="13" customHeight="1"/>
+    <row r="77" ht="13" customHeight="1"/>
+    <row r="78" ht="13" customHeight="1"/>
+    <row r="79" ht="13" customHeight="1"/>
+    <row r="80" ht="13" customHeight="1"/>
+    <row r="81" ht="13" customHeight="1"/>
+    <row r="82" ht="13" customHeight="1"/>
+    <row r="83" ht="13" customHeight="1"/>
+    <row r="84" ht="13" customHeight="1"/>
+    <row r="85" ht="13" customHeight="1"/>
+    <row r="86" ht="13" customHeight="1"/>
+    <row r="87" ht="13" customHeight="1"/>
+    <row r="88" ht="13" customHeight="1"/>
+    <row r="89" ht="13" customHeight="1"/>
+    <row r="90" ht="13" customHeight="1"/>
+    <row r="91" ht="13" customHeight="1"/>
+    <row r="92" ht="13" customHeight="1"/>
+    <row r="93" ht="13" customHeight="1"/>
+    <row r="94" ht="13" customHeight="1"/>
+    <row r="95" ht="13" customHeight="1"/>
+    <row r="96" ht="13" customHeight="1"/>
+    <row r="97" ht="13" customHeight="1"/>
+    <row r="98" ht="13" customHeight="1"/>
+    <row r="99" ht="13" customHeight="1"/>
+    <row r="100" ht="13" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A57:L57"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -782,6 +2026,11 @@
           <t>改訂履歴</t>
         </is>
       </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="27" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -875,6 +2124,11 @@
           <t>システム概要</t>
         </is>
       </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="27" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -882,6 +2136,11 @@
           <t>1. システム目的</t>
         </is>
       </c>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="27" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
@@ -889,6 +2148,11 @@
           <t xml:space="preserve">  • Windowsの名前付きパイプ（Named Pipe）を使用し、同一マシン上のプロセス間でコマンドを送受信するサーバー／クライアント通信基盤を提供する。</t>
         </is>
       </c>
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="26" t="n"/>
+      <c r="F4" s="27" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
@@ -896,6 +2160,11 @@
           <t xml:space="preserve">  • サーバーはRunspacePool（最大10スレッド）により、最大10クライアントの同時接続を処理する。</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="27" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
@@ -903,6 +2172,11 @@
           <t xml:space="preserve">  • 各クライアントセッションからOracle DBへのSELECT / DML操作をパイプ経由で実行できる。</t>
         </is>
       </c>
+      <c r="B6" s="26" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="27" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
@@ -910,6 +2184,11 @@
           <t xml:space="preserve">  • サーバーはStart / Stop / Statusパラメーターで制御可能なバックグラウンドプロセスとして動作する。</t>
         </is>
       </c>
+      <c r="B7" s="26" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="27" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -917,6 +2196,11 @@
           <t>2. コンポーネント構成</t>
         </is>
       </c>
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="27" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -1020,6 +2304,11 @@
           <t>3. 技術スタック</t>
         </is>
       </c>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="26" t="n"/>
+      <c r="F15" s="27" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -1233,6 +2522,12 @@
           <t>サーバー機能仕様　NamedPipeServer.ps1</t>
         </is>
       </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="26" t="n"/>
+      <c r="G1" s="27" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
@@ -1240,6 +2535,12 @@
           <t>1. 起動パラメーター (-Action)</t>
         </is>
       </c>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="26" t="n"/>
+      <c r="G3" s="27" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -1432,6 +2733,12 @@
           <t>2. 設定値一覧</t>
         </is>
       </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -1774,6 +3081,12 @@
           <t>3. 接続受付ループ仕様</t>
         </is>
       </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="27" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -1996,6 +3309,11 @@
           <t>パイプコマンド仕様</t>
         </is>
       </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="27" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
@@ -2003,6 +3321,11 @@
           <t>1. 一般コマンド</t>
         </is>
       </c>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="27" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -2162,6 +3485,11 @@
           <t>2. Oracle DBコマンド</t>
         </is>
       </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -2329,6 +3657,11 @@
           <t>3. レスポンスプロトコル</t>
         </is>
       </c>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="27" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
@@ -2341,6 +3674,10 @@
           <t>PING/TIME等のシンプルなコマンドは1行で返却し、続けて&lt;&lt;END&gt;&gt;を送信する</t>
         </is>
       </c>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="27" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
@@ -2353,6 +3690,10 @@
           <t>DBSTATUS/DBHELPなど複数行の場合、各行を個別に送信し最後に&lt;&lt;END&gt;&gt;を送信する</t>
         </is>
       </c>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="27" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
@@ -2365,6 +3706,10 @@
           <t>エラー時は「エラー: &lt;メッセージ&gt;」形式で1行返却し&lt;&lt;END&gt;&gt;を送信する</t>
         </is>
       </c>
+      <c r="C20" s="26" t="n"/>
+      <c r="D20" s="26" t="n"/>
+      <c r="E20" s="26" t="n"/>
+      <c r="F20" s="27" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="17" t="inlineStr">
@@ -2377,6 +3722,10 @@
           <t>接続直後にウェルカムメッセージを1行送信する（&lt;&lt;END&gt;&gt;なし）</t>
         </is>
       </c>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="27" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
@@ -2389,6 +3738,10 @@
           <t>サヨナラメッセージを1行送信後、サーバー側でパイプをDisconnect/Disposeする（&lt;&lt;END&gt;&gt;なし）</t>
         </is>
       </c>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2430,6 +3783,11 @@
           <t>クライアント機能仕様　NamedPipeClient.ps1</t>
         </is>
       </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="27" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="19" t="inlineStr">
@@ -2437,6 +3795,11 @@
           <t>1. 設定値一覧</t>
         </is>
       </c>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="27" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -2625,6 +3988,11 @@
           <t>2. 接続リトライ仕様</t>
         </is>
       </c>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
@@ -2786,6 +4154,11 @@
           <t>3. セッション処理仕様（Start-Session）</t>
         </is>
       </c>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="27" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
@@ -2946,6 +4319,11 @@
           <t>ログ仕様</t>
         </is>
       </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="27" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -2953,6 +4331,11 @@
           <t>1. ログファイル一覧</t>
         </is>
       </c>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="27" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -3088,6 +4471,11 @@
           <t>2. ログフォーマット</t>
         </is>
       </c>
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="27" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
@@ -3095,6 +4483,11 @@
           <t>[yyyy-MM-dd HH:mm:ss] [LEVEL] [C#&lt;ClientID&gt;] &lt;メッセージ&gt;</t>
         </is>
       </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="27" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
@@ -3102,6 +4495,11 @@
           <t>3. サーバーログ出力イベント一覧</t>
         </is>
       </c>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -3439,6 +4837,11 @@
           <t>4. クライアントログ出力イベント一覧</t>
         </is>
       </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+      <c r="E29" s="26" t="n"/>
+      <c r="F29" s="27" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -3762,6 +5165,11 @@
           <t>エラー処理仕様</t>
         </is>
       </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="27" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -3769,6 +5177,11 @@
           <t>1. サーバー側エラー処理</t>
         </is>
       </c>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="26" t="n"/>
+      <c r="F3" s="27" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -4019,6 +5432,11 @@
           <t>2. クライアント側エラー処理</t>
         </is>
       </c>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="26" t="n"/>
+      <c r="F14" s="27" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -4215,6 +5633,10 @@
           <t>制約・前提条件</t>
         </is>
       </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="27" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -4222,6 +5644,10 @@
           <t>1. 実行環境要件</t>
         </is>
       </c>
+      <c r="B3" s="26" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="E3" s="27" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -4246,6 +5672,9 @@
           <t>Windows OS（PowerShell 5.1が実行可能な環境）</t>
         </is>
       </c>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="27" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
@@ -4258,6 +5687,9 @@
           <t>5.1以上（#Requires -Version 5.1）</t>
         </is>
       </c>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="27" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -4270,6 +5702,9 @@
           <t>Bypass または RemoteSigned 以上</t>
         </is>
       </c>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="27" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
@@ -4282,6 +5717,9 @@
           <t>Oracle Client（ODP.NET Managed Driver）がインストール済みであること</t>
         </is>
       </c>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="27" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -4294,6 +5732,9 @@
           <t>Global\名前空間を使用するためサーバー起動に管理者権限が必要な場合あり</t>
         </is>
       </c>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="27" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -4301,6 +5742,10 @@
           <t>2. 接続制約</t>
         </is>
       </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="27" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -4325,6 +5770,9 @@
           <t>10（$MaxRunspacesで変更可能）</t>
         </is>
       </c>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="27" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
@@ -4337,6 +5785,9 @@
           <t>ローカルマシン内のみ（\\.\ pipe\\）。リモート接続は$ServerName変更で対応</t>
         </is>
       </c>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="27" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -4349,6 +5800,9 @@
           <t>同一パイプ名のサーバーを複数起動不可</t>
         </is>
       </c>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="27" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -4356,6 +5810,10 @@
           <t>3. セキュリティ制約</t>
         </is>
       </c>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="27" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -4380,6 +5838,9 @@
           <t>DBQUERYはSELECT / WITHのみ許可。DMLはDBEXECを使用すること</t>
         </is>
       </c>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="27" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
@@ -4392,6 +5853,9 @@
           <t>DBEXECへのSELECT文送信は拒否される</t>
         </is>
       </c>
+      <c r="C20" s="26" t="n"/>
+      <c r="D20" s="26" t="n"/>
+      <c r="E20" s="27" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -4404,6 +5868,9 @@
           <t>$OraclePasswordはスクリプト内に平文保存。本番環境ではSecureStringまたはVaultへの変更を推奨</t>
         </is>
       </c>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="27" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
@@ -4416,6 +5883,9 @@
           <t>デフォルトはローカル管理者権限ユーザーのみアクセス可能（Windowsパイプアクセス制御に依存）</t>
         </is>
       </c>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="27" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
@@ -4423,6 +5893,10 @@
           <t>4. パフォーマンス制約</t>
         </is>
       </c>
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="27" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
@@ -4447,6 +5921,9 @@
           <t>DBQUERYの返却行数は最大500行</t>
         </is>
       </c>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="27" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -4459,6 +5936,9 @@
           <t>30秒（$OracleQueryTimeoutで変更可能）</t>
         </is>
       </c>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+      <c r="E27" s="27" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
@@ -4471,6 +5951,9 @@
           <t>全スロット使用中の場合、新規クライアントは200msポーリングでスロット解放を待機する</t>
         </is>
       </c>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+      <c r="E28" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
